--- a/public/excel_files/sales-data-sample.xlsx
+++ b/public/excel_files/sales-data-sample.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28713"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\new-hyundi\public\excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\new-hyundi\public\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACDAC56-9E45-4351-89FC-A9D609D80CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>First Name</t>
   </si>
@@ -96,12 +97,15 @@
   </si>
   <si>
     <t>Customer Name</t>
+  </si>
+  <si>
+    <t>Inv No</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -427,25 +431,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="6" max="6" width="9.26953125" customWidth="1"/>
-    <col min="7" max="7" width="6.36328125" customWidth="1"/>
-    <col min="8" max="8" width="27.1796875" customWidth="1"/>
-    <col min="9" max="9" width="9.6328125" customWidth="1"/>
-    <col min="10" max="10" width="17.7265625" customWidth="1"/>
-    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" customWidth="1"/>
+    <col min="8" max="8" width="27.21875" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" customWidth="1"/>
+    <col min="10" max="10" width="17.77734375" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -482,8 +486,11 @@
       <c r="L1" t="s">
         <v>13</v>
       </c>
+      <c r="M1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -520,8 +527,11 @@
       <c r="L2" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="M2">
+        <v>101019226</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -557,12 +567,15 @@
       </c>
       <c r="L3" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="M3">
+        <v>101016903</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
-    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId3"/>

--- a/public/excel_files/sales-data-sample.xlsx
+++ b/public/excel_files/sales-data-sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\new-hyundi\public\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACDAC56-9E45-4351-89FC-A9D609D80CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D230B565-7E6B-4286-AC56-32BEDC96F010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>First Name</t>
   </si>
@@ -88,15 +88,6 @@
   </si>
   <si>
     <t>ELANTRA</t>
-  </si>
-  <si>
-    <t>Saudi Doors Factory</t>
-  </si>
-  <si>
-    <t>Dhaifallah Abdulmohsen Al - Fr</t>
-  </si>
-  <si>
-    <t>Customer Name</t>
   </si>
   <si>
     <t>Inv No</t>
@@ -432,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -444,12 +435,11 @@
     <col min="7" max="7" width="6.33203125" customWidth="1"/>
     <col min="8" max="8" width="27.21875" customWidth="1"/>
     <col min="9" max="9" width="9.6640625" customWidth="1"/>
-    <col min="10" max="10" width="17.77734375" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -478,19 +468,16 @@
         <v>11</v>
       </c>
       <c r="J1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -518,20 +505,17 @@
       <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="3">
+      <c r="J2" s="3">
         <v>563063041</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M2">
+      <c r="L2">
         <v>101019226</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -559,16 +543,13 @@
       <c r="I3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="3">
+      <c r="J3" s="3">
         <v>595566939</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M3">
+      <c r="L3">
         <v>101016903</v>
       </c>
     </row>

--- a/public/excel_files/sales-data-sample.xlsx
+++ b/public/excel_files/sales-data-sample.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\new-hyundi\public\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D230B565-7E6B-4286-AC56-32BEDC96F010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533CA7DE-35A7-4819-977B-7D230911B044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>First Name</t>
   </si>
@@ -33,10 +28,31 @@
     <t>Last Name</t>
   </si>
   <si>
+    <t>Email</t>
+  </si>
+  <si>
     <t>Mobile</t>
   </si>
   <si>
-    <t>Email</t>
+    <t>INV Date</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Chass</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Inv No</t>
   </si>
   <si>
     <t>Ateeb</t>
@@ -48,56 +64,32 @@
     <t>ateeb@sohoby.ae</t>
   </si>
   <si>
-    <t>INV Date</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>Chass</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>Gender</t>
+    <t>f</t>
+  </si>
+  <si>
+    <t>KMJYA3714NU023243</t>
+  </si>
+  <si>
+    <t>STARIA</t>
   </si>
   <si>
     <t>Male</t>
   </si>
   <si>
-    <t>f</t>
-  </si>
-  <si>
     <t>s</t>
   </si>
   <si>
-    <t>KMJYA3714NU023243</t>
-  </si>
-  <si>
     <t>KMHLN41E4NU284941</t>
   </si>
   <si>
-    <t>STARIA</t>
-  </si>
-  <si>
     <t>ELANTRA</t>
-  </si>
-  <si>
-    <t>Inv No</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,10 +100,15 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -122,7 +119,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -131,24 +135,45 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -195,15 +220,15 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -238,7 +263,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -282,164 +307,189 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
                 <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" customWidth="1"/>
-    <col min="6" max="6" width="9.21875" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" customWidth="1"/>
-    <col min="8" max="8" width="27.21875" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" customWidth="1"/>
-    <col min="10" max="10" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,118 +497,104 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="L1" t="s">
-        <v>21</v>
+      <c r="D2" s="6">
+        <v>966530634870</v>
+      </c>
+      <c r="E2" s="7">
+        <v>44636</v>
+      </c>
+      <c r="F2" s="8">
+        <v>2022</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="6">
+        <v>101019226</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
+    <row r="3" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="6">
         <v>966530634870</v>
       </c>
-      <c r="E2" s="2">
-        <v>44636</v>
-      </c>
-      <c r="F2" s="3">
-        <v>2022</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="E3" s="7">
+        <v>45001</v>
+      </c>
+      <c r="F3" s="8">
+        <v>2023</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="3">
-        <v>563063041</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2">
-        <v>101019226</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>966530634870</v>
-      </c>
-      <c r="E3" s="2">
-        <v>45001</v>
-      </c>
-      <c r="F3" s="3">
-        <v>2023</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="3">
-        <v>595566939</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3">
+      <c r="K3" s="6">
         <v>101016903</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId3"/>
 </worksheet>
 </file>